--- a/reference/Ormoc_CDRRMO_EOC_Master_Requirements_Traceability_and_140_Indicator_Data_Dictionary_v1.1.xlsx
+++ b/reference/Ormoc_CDRRMO_EOC_Master_Requirements_Traceability_and_140_Indicator_Data_Dictionary_v1.1.xlsx
@@ -1653,7 +1653,7 @@
     <t xml:space="preserve">A3.7</t>
   </si>
   <si>
-    <t xml:space="preserve">Barangay DRRM plans (110 barangays) reviewed/consolidated by CDRRMO</t>
+    <t xml:space="preserve">Barangay DRRM plans (85 barangays) reviewed/consolidated by CDRRMO</t>
   </si>
   <si>
     <t xml:space="preserve">RA 10121 Sec. 12(c)(6); DILG MC on BDRRM</t>
@@ -2052,7 +2052,7 @@
     <t xml:space="preserve">A7.3</t>
   </si>
   <si>
-    <t xml:space="preserve">BDRRMC functionality across 110 barangays assessed (e.g., Listo si KAP) with support plan for low-functioning barangays</t>
+    <t xml:space="preserve">BDRRMC functionality across 85 barangays assessed (e.g., Listo si KAP) with support plan for low-functioning barangays</t>
   </si>
   <si>
     <t xml:space="preserve">RA 10121; DILG MC 2025-035 (Listo si KAP)</t>
@@ -2652,7 +2652,7 @@
     <t xml:space="preserve">B3.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Radio network covering all 110 barangays and responders, with call signs and net-control procedure</t>
+    <t xml:space="preserve">Radio network covering all 85 barangays and responders, with call signs and net-control procedure</t>
   </si>
   <si>
     <t xml:space="preserve">NTC licensing; ETC cluster</t>
